--- a/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
+++ b/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
@@ -1074,7 +1074,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">

--- a/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
+++ b/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
@@ -1074,7 +1074,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2389,34 +2389,34 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>21663000</v>
+        <v>19821000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>38615</v>
+        <v>35332</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>20579850</v>
+        <v>19821000</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>36684</v>
+        <v>35332</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減5%) + 120天提前成交現金回贈6%</t>
+          <t>建築期備⽤⼀按貸款付款計劃</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8032,12 +8032,12 @@
       <c r="E6" s="20" t="inlineStr"/>
       <c r="F6" s="20" t="inlineStr"/>
       <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
-$2166万
-$38,615/呎
-(在售)</t>
+$1982万
+$35,332/呎
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -8045,7 +8045,7 @@
           <t>E2 | 435呎 (2房)
 $1547万
 $35,554/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -8077,7 +8077,7 @@
           <t>E7 | 515呎 (2房)
 $1880万
 $36,515/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr"/>
@@ -8094,7 +8094,7 @@
           <t>G3 | 502呎 (2房)
 $1775万
 $35,357/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="Q6" s="22" t="inlineStr">
@@ -8119,7 +8119,7 @@
           <t>S1 | 1294呎 (4+房)
 $5241万
 $40,500/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="U6" s="23" t="inlineStr">
@@ -8127,7 +8127,7 @@
           <t>S2 | 981呎 (3房)
 $4169万
 $42,500/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="V6" s="20" t="inlineStr"/>
@@ -8143,7 +8143,7 @@
           <t>D1 | 1612呎 (4+房)
 $6287万
 $39,000/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -8151,7 +8151,7 @@
           <t>D2 | 1642呎 (4+房)
 $7739万
 $47,132/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -8159,7 +8159,7 @@
           <t>D3 | 1593呎 (4+房)
 $7628万
 $47,883/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -8167,7 +8167,7 @@
           <t>D5 | 1595呎 (4+房)
 $8325万
 $52,194/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -8175,7 +8175,7 @@
           <t>D6 | 1596呎 (4+房)
 $8330万
 $52,193/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -8212,7 +8212,7 @@
           <t>S3 | 1608呎 (4+房)
 $9144万
 $56,866/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
           <t>E2 | 435呎 (2房)
 $1589万
 $36,522/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -8273,7 +8273,7 @@
           <t>E7 | 515呎 (2房)
 $1844万
 $35,800/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr"/>
@@ -8290,7 +8290,7 @@
           <t>G3 | 585呎 (2房)
 $2028万
 $34,663/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="Q8" s="22" t="inlineStr">
@@ -8306,7 +8306,7 @@
           <t>G6 | 1135呎 (4+房)
 $4086万
 $36,000/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="S8" s="20" t="inlineStr"/>
@@ -8315,7 +8315,7 @@
           <t>S1 | 1294呎 (4+房)
 $5952万
 $46,000/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="U8" s="23" t="inlineStr">
@@ -8323,7 +8323,7 @@
           <t>S2 | 1061呎 (3房)
 $4615万
 $43,500/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="V8" s="20" t="inlineStr"/>
@@ -8345,7 +8345,7 @@
           <t>E1 | 561呎 (2房)
 $1905万
 $33,961/呎
-(26年-07月-06日)</t>
+(26年-07月-27日)</t>
         </is>
       </c>
       <c r="I9" s="23" t="inlineStr">
@@ -8353,7 +8353,7 @@
           <t>E2 | 435呎 (2房)
 $1487万
 $34,175/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">
@@ -8361,7 +8361,7 @@
           <t>E3 | 469呎 (2房)
 $1547万
 $32,991/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -8385,7 +8385,7 @@
           <t>E7 | 515呎 (2房)
 $1807万
 $35,095/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr"/>
@@ -8394,7 +8394,7 @@
           <t>G2 | 976呎 (3房)
 $4002万
 $41,000/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="P9" s="23" t="inlineStr">
@@ -8402,7 +8402,7 @@
           <t>G3 | 502呎 (2房)
 $1710万
 $34,066/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="Q9" s="22" t="inlineStr">
@@ -8418,7 +8418,7 @@
           <t>G6 | 1135呎 (4+房)
 $3859万
 $34,000/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="S9" s="20" t="inlineStr"/>
@@ -8427,7 +8427,7 @@
           <t>S1 | 1294呎 (4+房)
 $5823万
 $45,000/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="U9" s="22" t="inlineStr">
@@ -8451,7 +8451,7 @@
           <t>D1 | 1596呎 (4+房)
 $6384万
 $40,000/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -8459,7 +8459,7 @@
           <t>D2 | 1605呎 (4+房)
 $4815万
 $30,000/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -8467,7 +8467,7 @@
           <t>D3 | 1576呎 (4+房)
 $5358万
 $34,000/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -8475,7 +8475,7 @@
           <t>D5 | 1581呎 (4+房)
 $4933万
 $31,200/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -8483,7 +8483,7 @@
           <t>D6 | 1579呎 (4+房)
 $5211万
 $33,000/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
@@ -8491,7 +8491,7 @@
           <t>D7 | 1584呎 (4+房)
 $6019万
 $38,000/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr"/>
@@ -8520,7 +8520,7 @@
           <t>S3 | 1590呎 (4+房)
 $6678万
 $42,000/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
     </row>
@@ -8549,7 +8549,7 @@
           <t>E2 | 435呎 (2房)
 $1458万
 $33,506/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -8557,7 +8557,7 @@
           <t>E3 | 469呎 (2房)
 $1517万
 $32,345/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="K11" s="23" t="inlineStr">
@@ -8565,7 +8565,7 @@
           <t>E5 | 336呎 (1房)
 $1090万
 $32,452/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="L11" s="22" t="inlineStr">
@@ -8581,7 +8581,7 @@
           <t>E7 | 515呎 (2房)
 $1763万
 $34,241/呎
-(26年-07月-01日)</t>
+(26年-07月-27日)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr"/>
@@ -8590,7 +8590,7 @@
           <t>G2 | 976呎 (3房)
 $3904万
 $40,000/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="P11" s="23" t="inlineStr">
@@ -8598,7 +8598,7 @@
           <t>G3 | 585呎 (2房)
 $1954万
 $33,397/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="Q11" s="22" t="inlineStr">
@@ -8614,7 +8614,7 @@
           <t>G6 | 1135呎 (4+房)
 $3836万
 $33,800/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="S11" s="20" t="inlineStr"/>
@@ -8623,7 +8623,7 @@
           <t>S1 | 1294呎 (4+房)
 $5047万
 $39,000/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="U11" s="22" t="inlineStr">
@@ -8661,7 +8661,7 @@
           <t>E2 | 435呎 (2房)
 $1432万
 $32,931/呎
-(26年-07月-20日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
@@ -8693,7 +8693,7 @@
           <t>E7 | 477呎 (2房)
 $1797万
 $37,665/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr"/>
@@ -8710,7 +8710,7 @@
           <t>G3 | 502呎 (2房)
 $1648万
 $32,825/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="Q12" s="22" t="inlineStr">
@@ -8726,7 +8726,7 @@
           <t>G6 | 1135呎 (4+房)
 $4670万
 $41,143/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="S12" s="20" t="inlineStr"/>
@@ -8735,7 +8735,7 @@
           <t>S1 | 1294呎 (4+房)
 $5694万
 $44,000/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="U12" s="22" t="inlineStr">
@@ -8759,7 +8759,7 @@
           <t>D1 | 1596呎 (4+房)
 $6065万
 $38,000/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -8767,7 +8767,7 @@
           <t>D2 | 1605呎 (4+房)
 $4687万
 $29,200/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -8775,7 +8775,7 @@
           <t>D3 | 1576呎 (4+房)
 $5834万
 $37,021/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -8783,7 +8783,7 @@
           <t>D5 | 1581呎 (4+房)
 $4743万
 $30,000/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -8791,7 +8791,7 @@
           <t>D6 | 1579呎 (4+房)
 $4978万
 $31,525/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
@@ -8799,7 +8799,7 @@
           <t>D7 | 1584呎 (4+房)
 $4752万
 $30,000/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr"/>
@@ -8813,7 +8813,7 @@
           <t>G1 | 2184呎 (4+房)
 $8387万
 $38,403/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr"/>
@@ -8828,7 +8828,7 @@
           <t>S3 | 1590呎 (4+房)
 $6519万
 $41,000/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -8870,57 +8870,15 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr"/>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
       <c r="H15" s="20" t="inlineStr"/>
       <c r="I15" s="20" t="inlineStr"/>
       <c r="J15" s="20" t="inlineStr"/>
@@ -8929,9 +8887,30 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="20" t="inlineStr"/>
-      <c r="Q15" s="20" t="inlineStr"/>
-      <c r="R15" s="20" t="inlineStr"/>
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q15" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
       <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
@@ -8940,15 +8919,57 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8957,30 +8978,9 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="Q16" s="22" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R16" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-28日)</t>
-        </is>
-      </c>
+      <c r="P16" s="20" t="inlineStr"/>
+      <c r="Q16" s="20" t="inlineStr"/>
+      <c r="R16" s="20" t="inlineStr"/>
       <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
@@ -9011,7 +9011,7 @@
           <t>G3 | 467呎 (2房)
 $1795万
 $38,428/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="Q17" s="22" t="inlineStr">
@@ -9027,7 +9027,7 @@
           <t>G6 | 1160呎 (4+房)
 $5220万
 $45,000/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="S17" s="20" t="inlineStr"/>

--- a/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
+++ b/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
@@ -8835,15 +8835,57 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8855,14 +8897,7 @@
       <c r="P14" s="20" t="inlineStr"/>
       <c r="Q14" s="20" t="inlineStr"/>
       <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="22" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
+      <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -8870,7 +8905,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B&amp;G&amp;1</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr"/>
@@ -8887,31 +8922,17 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q15" s="22" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
+      <c r="P15" s="20" t="inlineStr"/>
+      <c r="Q15" s="20" t="inlineStr"/>
+      <c r="R15" s="20" t="inlineStr"/>
+      <c r="S15" s="22" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="R15" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -8919,57 +8940,15 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8978,9 +8957,30 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="20" t="inlineStr"/>
-      <c r="Q16" s="20" t="inlineStr"/>
-      <c r="R16" s="20" t="inlineStr"/>
+      <c r="P16" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q16" s="22" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R16" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
       <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>

--- a/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
+++ b/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
@@ -8331,16 +8331,100 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5&amp;6</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6384万
+$40,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4815万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5358万
+$34,000/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4933万
+$31,200/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$5211万
+$33,000/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$6019万
+$38,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+      <c r="K9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
+      <c r="N9" s="22" t="inlineStr">
+        <is>
+          <t>G1 | 2185呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr"/>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr"/>
+      <c r="V9" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6678万
+$42,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1905万
@@ -8348,7 +8432,7 @@
 (26年-07月-27日)</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1487万
@@ -8356,7 +8440,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1547万
@@ -8364,7 +8448,7 @@
 (26年-07月-13日)</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1222万
@@ -8372,7 +8456,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L9" s="21" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1634万
@@ -8380,7 +8464,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1807万
@@ -8388,8 +8472,8 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="23" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr"/>
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 $4002万
@@ -8397,7 +8481,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="P9" s="23" t="inlineStr">
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1710万
@@ -8405,7 +8489,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="Q10" s="22" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8413,7 +8497,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R9" s="23" t="inlineStr">
+      <c r="R10" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $3859万
@@ -8421,8 +8505,8 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="23" t="inlineStr">
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5823万
@@ -8430,7 +8514,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U9" s="22" t="inlineStr">
+      <c r="U10" s="22" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8438,91 +8522,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5&amp;6</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6384万
-$40,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4815万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5358万
-$34,000/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4933万
-$31,200/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$5211万
-$33,000/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$6019万
-$38,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr"/>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
-      <c r="K10" s="20" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr"/>
-      <c r="M10" s="20" t="inlineStr"/>
-      <c r="N10" s="22" t="inlineStr">
-        <is>
-          <t>G1 | 2185呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="20" t="inlineStr"/>
-      <c r="Q10" s="20" t="inlineStr"/>
-      <c r="R10" s="20" t="inlineStr"/>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="20" t="inlineStr"/>
-      <c r="U10" s="20" t="inlineStr"/>
-      <c r="V10" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6678万
-$42,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
+      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -8639,16 +8639,100 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6065万
+$38,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4687万
+$29,200/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5834万
+$37,021/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4743万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$4978万
+$31,525/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$4752万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+      <c r="K12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr"/>
+      <c r="M12" s="20" t="inlineStr"/>
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+$8387万
+$38,403/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr"/>
+      <c r="P12" s="20" t="inlineStr"/>
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6519万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1992万
@@ -8656,7 +8740,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I12" s="23" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1432万
@@ -8664,7 +8748,7 @@
 (26年-07月-21日)</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1618万
@@ -8672,7 +8756,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>E5 | 298呎 (1房)
 $1104万
@@ -8680,7 +8764,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L12" s="22" t="inlineStr">
+      <c r="L13" s="22" t="inlineStr">
         <is>
           <t>E6 | 397呎 (2房)
 $1633万
@@ -8688,7 +8772,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M12" s="23" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t>E7 | 477呎 (2房)
 $1797万
@@ -8696,8 +8780,8 @@
 (26年-07月-23日)</t>
         </is>
       </c>
-      <c r="N12" s="20" t="inlineStr"/>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="N13" s="20" t="inlineStr"/>
+      <c r="O13" s="22" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8705,7 +8789,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P12" s="23" t="inlineStr">
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1648万
@@ -8713,7 +8797,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="Q13" s="22" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8721,7 +8805,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R12" s="23" t="inlineStr">
+      <c r="R13" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $4670万
@@ -8729,8 +8813,8 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="23" t="inlineStr">
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5694万
@@ -8738,7 +8822,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U12" s="22" t="inlineStr">
+      <c r="U13" s="22" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8746,91 +8830,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>2&amp;3</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6065万
-$38,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4687万
-$29,200/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5834万
-$37,021/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4743万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$4978万
-$31,525/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$4752万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr"/>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
-      <c r="K13" s="20" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr"/>
-      <c r="M13" s="20" t="inlineStr"/>
-      <c r="N13" s="23" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-$8387万
-$38,403/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="O13" s="20" t="inlineStr"/>
-      <c r="P13" s="20" t="inlineStr"/>
-      <c r="Q13" s="20" t="inlineStr"/>
-      <c r="R13" s="20" t="inlineStr"/>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="20" t="inlineStr"/>
-      <c r="U13" s="20" t="inlineStr"/>
-      <c r="V13" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6519万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+      <c r="V13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">

--- a/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
+++ b/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
@@ -116,13 +116,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
     <font>
@@ -269,10 +269,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -7925,10 +7925,10 @@
           <t>E1 | 560呎 (2房)
 $2206万
 $39,388/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I5" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1724万
@@ -7936,7 +7936,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1795万
@@ -7944,7 +7944,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K5" s="21" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1296万
@@ -7952,7 +7952,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L5" s="21" t="inlineStr">
+      <c r="L5" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1734万
@@ -7965,11 +7965,11 @@
           <t>E7 | 515呎 (2房)
 $2096万
 $40,707/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="N5" s="20" t="inlineStr"/>
-      <c r="O5" s="22" t="inlineStr">
+      <c r="O5" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -7977,7 +7977,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P5" s="22" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t>G3 | 584呎 (2房)
 $2296万
@@ -7985,7 +7985,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="Q5" s="22" t="inlineStr">
+      <c r="Q5" s="21" t="inlineStr">
         <is>
           <t>G5 | 868呎 (3房)
 招标单位
@@ -7993,7 +7993,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R5" s="22" t="inlineStr">
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t>G6 | 1158呎 (4+房)
 招标单位
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="S5" s="20" t="inlineStr"/>
-      <c r="T5" s="22" t="inlineStr">
+      <c r="T5" s="21" t="inlineStr">
         <is>
           <t>S1 | 1320呎 (4+房)
 招标单位
@@ -8010,7 +8010,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="U5" s="22" t="inlineStr">
+      <c r="U5" s="21" t="inlineStr">
         <is>
           <t>S2 | 1060呎 (3房)
 招标单位
@@ -8023,16 +8023,100 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7&amp;8</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1612呎 (4+房)
+$6287万
+$39,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1642呎 (4+房)
+$7739万
+$47,132/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1593呎 (4+房)
+$7628万
+$47,883/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1595呎 (4+房)
+$8325万
+$52,194/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1596呎 (4+房)
+$8330万
+$52,193/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>D7 | 1602呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1608呎 (4+房)
+$9144万
+$56,866/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1982万
@@ -8040,7 +8124,7 @@
 (26年-07月-30日)</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1547万
@@ -8048,7 +8132,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="J6" s="21" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1760万
@@ -8056,7 +8140,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1271万
@@ -8064,7 +8148,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L6" s="21" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1700万
@@ -8072,7 +8156,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1880万
@@ -8080,8 +8164,8 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8089,7 +8173,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1775万
@@ -8097,7 +8181,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8105,7 +8189,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R6" s="22" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 招标单位
@@ -8113,8 +8197,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="23" t="inlineStr">
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5241万
@@ -8122,7 +8206,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U6" s="23" t="inlineStr">
+      <c r="U7" s="23" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 $4169万
@@ -8130,91 +8214,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="V6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7&amp;8</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1612呎 (4+房)
-$6287万
-$39,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1642呎 (4+房)
-$7739万
-$47,132/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1593呎 (4+房)
-$7628万
-$47,883/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1595呎 (4+房)
-$8325万
-$52,194/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1596呎 (4+房)
-$8330万
-$52,193/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="G7" s="22" t="inlineStr">
-        <is>
-          <t>D7 | 1602呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
-      <c r="K7" s="20" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr"/>
-      <c r="M7" s="20" t="inlineStr"/>
-      <c r="N7" s="22" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O7" s="20" t="inlineStr"/>
-      <c r="P7" s="20" t="inlineStr"/>
-      <c r="Q7" s="20" t="inlineStr"/>
-      <c r="R7" s="20" t="inlineStr"/>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="20" t="inlineStr"/>
-      <c r="U7" s="20" t="inlineStr"/>
-      <c r="V7" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1608呎 (4+房)
-$9144万
-$56,866/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8233,7 +8233,7 @@
           <t>E1 | 561呎 (2房)
 $2124万
 $37,857/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -8244,7 +8244,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1725万
@@ -8252,7 +8252,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K8" s="22" t="inlineStr">
+      <c r="K8" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1246万
@@ -8260,7 +8260,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L8" s="22" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1667万
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr"/>
-      <c r="O8" s="22" t="inlineStr">
+      <c r="O8" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8293,7 +8293,7 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="Q8" s="22" t="inlineStr">
+      <c r="Q8" s="21" t="inlineStr">
         <is>
           <t>G5 | 868呎 (3房)
 招标单位
@@ -8388,7 +8388,7 @@
       <c r="K9" s="20" t="inlineStr"/>
       <c r="L9" s="20" t="inlineStr"/>
       <c r="M9" s="20" t="inlineStr"/>
-      <c r="N9" s="22" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t>G1 | 2185呎 (4+房)
 招标单位
@@ -8448,7 +8448,7 @@
 (26年-07月-13日)</t>
         </is>
       </c>
-      <c r="K10" s="21" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1222万
@@ -8456,7 +8456,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L10" s="21" t="inlineStr">
+      <c r="L10" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1634万
@@ -8489,7 +8489,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="Q10" s="22" t="inlineStr">
+      <c r="Q10" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8514,7 +8514,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U10" s="22" t="inlineStr">
+      <c r="U10" s="21" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8536,7 +8536,7 @@
       <c r="E11" s="20" t="inlineStr"/>
       <c r="F11" s="20" t="inlineStr"/>
       <c r="G11" s="20" t="inlineStr"/>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $2041万
@@ -8568,7 +8568,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="L11" s="22" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1594万
@@ -8601,7 +8601,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="Q11" s="22" t="inlineStr">
+      <c r="Q11" s="21" t="inlineStr">
         <is>
           <t>G5 | 868呎 (3房)
 招标单位
@@ -8626,7 +8626,7 @@
 (26年-07月-03日)</t>
         </is>
       </c>
-      <c r="U11" s="22" t="inlineStr">
+      <c r="U11" s="21" t="inlineStr">
         <is>
           <t>S2 | 1061呎 (3房)
 招标单位
@@ -8732,7 +8732,7 @@
       <c r="E13" s="20" t="inlineStr"/>
       <c r="F13" s="20" t="inlineStr"/>
       <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1992万
@@ -8748,7 +8748,7 @@
 (26年-07月-21日)</t>
         </is>
       </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1618万
@@ -8756,7 +8756,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K13" s="21" t="inlineStr">
         <is>
           <t>E5 | 298呎 (1房)
 $1104万
@@ -8764,7 +8764,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L13" s="22" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t>E6 | 397呎 (2房)
 $1633万
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr"/>
-      <c r="O13" s="22" t="inlineStr">
+      <c r="O13" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8797,7 +8797,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="Q13" s="22" t="inlineStr">
+      <c r="Q13" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8822,7 +8822,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U13" s="22" t="inlineStr">
+      <c r="U13" s="21" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8835,57 +8835,15 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8894,9 +8852,30 @@
       <c r="M14" s="20" t="inlineStr"/>
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="20" t="inlineStr"/>
-      <c r="Q14" s="20" t="inlineStr"/>
-      <c r="R14" s="20" t="inlineStr"/>
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q14" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R14" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
       <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
@@ -8905,15 +8884,57 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr"/>
-      <c r="C15" s="20" t="inlineStr"/>
-      <c r="D15" s="20" t="inlineStr"/>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H15" s="20" t="inlineStr"/>
       <c r="I15" s="20" t="inlineStr"/>
       <c r="J15" s="20" t="inlineStr"/>
@@ -8925,14 +8946,7 @@
       <c r="P15" s="20" t="inlineStr"/>
       <c r="Q15" s="20" t="inlineStr"/>
       <c r="R15" s="20" t="inlineStr"/>
-      <c r="S15" s="22" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
+      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -8940,7 +8954,7 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B&amp;G&amp;1</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr"/>
@@ -8957,31 +8971,17 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q16" s="22" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
+      <c r="P16" s="20" t="inlineStr"/>
+      <c r="Q16" s="20" t="inlineStr"/>
+      <c r="R16" s="20" t="inlineStr"/>
+      <c r="S16" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="R16" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
       <c r="V16" s="20" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
 (26年-07月-13日)</t>
         </is>
       </c>
-      <c r="Q17" s="22" t="inlineStr">
+      <c r="Q17" s="21" t="inlineStr">
         <is>
           <t>G5 | 831呎 (3房)
 招标单位

--- a/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
+++ b/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
@@ -6259,34 +6259,34 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
-        <v>11042000</v>
+        <v>10103000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>37054</v>
+        <v>33903</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="5" t="n">
-        <v>10489900</v>
+        <v>10103000</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>35201</v>
+        <v>33903</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>建築期備⽤⼀按貸款付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8023,10 +8023,122 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1982万
+$35,332/呎
+(26年-07月-30日)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1547万
+$35,554/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1760万
+$37,516/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1271万
+$37,821/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1700万
+$39,171/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1880万
+$36,515/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1775万
+$35,357/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5241万
+$40,500/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U6" s="23" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+$4169万
+$42,500/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="V6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7&amp;8</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>D1 | 1612呎 (4+房)
 $6287万
@@ -8034,7 +8146,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>D2 | 1642呎 (4+房)
 $7739万
@@ -8042,7 +8154,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>D3 | 1593呎 (4+房)
 $7628万
@@ -8050,7 +8162,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D5 | 1595呎 (4+房)
 $8325万
@@ -8058,7 +8170,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>D6 | 1596呎 (4+房)
 $8330万
@@ -8066,7 +8178,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>D7 | 1602呎 (4+房)
 招标单位
@@ -8074,13 +8186,13 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-      <c r="K6" s="20" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr"/>
-      <c r="M6" s="20" t="inlineStr"/>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 招标单位
@@ -8088,14 +8200,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O6" s="20" t="inlineStr"/>
-      <c r="P6" s="20" t="inlineStr"/>
-      <c r="Q6" s="20" t="inlineStr"/>
-      <c r="R6" s="20" t="inlineStr"/>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="20" t="inlineStr"/>
-      <c r="V6" s="23" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="23" t="inlineStr">
         <is>
           <t>S3 | 1608呎 (4+房)
 $9144万
@@ -8103,118 +8215,6 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1982万
-$35,332/呎
-(26年-07月-30日)</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1547万
-$35,554/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1760万
-$37,516/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K7" s="22" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1271万
-$37,821/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L7" s="22" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1700万
-$39,171/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M7" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1880万
-$36,515/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="21" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1775万
-$35,357/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q7" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5241万
-$40,500/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U7" s="23" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-$4169万
-$42,500/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8756,12 +8756,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K13" s="21" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>E5 | 298呎 (1房)
-$1104万
-$37,054/呎
-(在售)</t>
+$1010万
+$33,903/呎
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">

--- a/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
+++ b/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
@@ -8023,16 +8023,100 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7&amp;8</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1612呎 (4+房)
+$6287万
+$39,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1642呎 (4+房)
+$7739万
+$47,132/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1593呎 (4+房)
+$7628万
+$47,883/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1595呎 (4+房)
+$8325万
+$52,194/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1596呎 (4+房)
+$8330万
+$52,193/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>D7 | 1602呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1608呎 (4+房)
+$9144万
+$56,866/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1982万
@@ -8040,7 +8124,7 @@
 (26年-07月-30日)</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1547万
@@ -8048,7 +8132,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1760万
@@ -8056,7 +8140,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1271万
@@ -8064,7 +8148,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1700万
@@ -8072,7 +8156,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1880万
@@ -8080,8 +8164,8 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="21" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8089,7 +8173,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1775万
@@ -8097,7 +8181,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="Q6" s="21" t="inlineStr">
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8105,7 +8189,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R6" s="21" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 招标单位
@@ -8113,8 +8197,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="23" t="inlineStr">
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5241万
@@ -8122,7 +8206,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U6" s="23" t="inlineStr">
+      <c r="U7" s="23" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 $4169万
@@ -8130,91 +8214,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="V6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7&amp;8</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1612呎 (4+房)
-$6287万
-$39,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1642呎 (4+房)
-$7739万
-$47,132/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1593呎 (4+房)
-$7628万
-$47,883/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1595呎 (4+房)
-$8325万
-$52,194/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1596呎 (4+房)
-$8330万
-$52,193/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>D7 | 1602呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
-      <c r="K7" s="20" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr"/>
-      <c r="M7" s="20" t="inlineStr"/>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O7" s="20" t="inlineStr"/>
-      <c r="P7" s="20" t="inlineStr"/>
-      <c r="Q7" s="20" t="inlineStr"/>
-      <c r="R7" s="20" t="inlineStr"/>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="20" t="inlineStr"/>
-      <c r="U7" s="20" t="inlineStr"/>
-      <c r="V7" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1608呎 (4+房)
-$9144万
-$56,866/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8639,10 +8639,122 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1992万
+$35,499/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1432万
+$32,931/呎
+(26年-07月-21日)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1618万
+$34,490/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>E5 | 298呎 (1房)
+$1010万
+$33,903/呎
+(26年-08月-12日)</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>E6 | 397呎 (2房)
+$1633万
+$41,141/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M12" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 477呎 (2房)
+$1797万
+$37,665/呎
+(26年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="N12" s="20" t="inlineStr"/>
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P12" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1648万
+$32,825/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="Q12" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R12" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$4670万
+$41,143/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5694万
+$44,000/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U12" s="21" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>2&amp;3</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>D1 | 1596呎 (4+房)
 $6065万
@@ -8650,7 +8762,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>D2 | 1605呎 (4+房)
 $4687万
@@ -8658,7 +8770,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>D3 | 1576呎 (4+房)
 $5834万
@@ -8666,7 +8778,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D5 | 1581呎 (4+房)
 $4743万
@@ -8674,7 +8786,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>D6 | 1579呎 (4+房)
 $4978万
@@ -8682,7 +8794,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>D7 | 1584呎 (4+房)
 $4752万
@@ -8690,13 +8802,13 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-      <c r="K12" s="20" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr"/>
-      <c r="M12" s="20" t="inlineStr"/>
-      <c r="N12" s="23" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
+      <c r="K13" s="20" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr"/>
+      <c r="M13" s="20" t="inlineStr"/>
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 $8387万
@@ -8704,14 +8816,14 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="O12" s="20" t="inlineStr"/>
-      <c r="P12" s="20" t="inlineStr"/>
-      <c r="Q12" s="20" t="inlineStr"/>
-      <c r="R12" s="20" t="inlineStr"/>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="20" t="inlineStr"/>
-      <c r="U12" s="20" t="inlineStr"/>
-      <c r="V12" s="23" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr"/>
+      <c r="P13" s="20" t="inlineStr"/>
+      <c r="Q13" s="20" t="inlineStr"/>
+      <c r="R13" s="20" t="inlineStr"/>
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="20" t="inlineStr"/>
+      <c r="U13" s="20" t="inlineStr"/>
+      <c r="V13" s="23" t="inlineStr">
         <is>
           <t>S3 | 1590呎 (4+房)
 $6519万
@@ -8720,130 +8832,60 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="20" t="inlineStr"/>
-      <c r="D13" s="20" t="inlineStr"/>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1992万
-$35,499/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I13" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1432万
-$32,931/呎
-(26年-07月-21日)</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1618万
-$34,490/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K13" s="23" t="inlineStr">
-        <is>
-          <t>E5 | 298呎 (1房)
-$1010万
-$33,903/呎
-(26年-08月-12日)</t>
-        </is>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t>E6 | 397呎 (2房)
-$1633万
-$41,141/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M13" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 477呎 (2房)
-$1797万
-$37,665/呎
-(26年-07月-23日)</t>
-        </is>
-      </c>
-      <c r="N13" s="20" t="inlineStr"/>
-      <c r="O13" s="21" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P13" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1648万
-$32,825/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="Q13" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R13" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$4670万
-$41,143/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5694万
-$44,000/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U13" s="21" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V13" s="20" t="inlineStr"/>
-    </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8852,30 +8894,9 @@
       <c r="M14" s="20" t="inlineStr"/>
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q14" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R14" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="P14" s="20" t="inlineStr"/>
+      <c r="Q14" s="20" t="inlineStr"/>
+      <c r="R14" s="20" t="inlineStr"/>
       <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
@@ -8884,57 +8905,15 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>B&amp;G&amp;1</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr"/>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
       <c r="H15" s="20" t="inlineStr"/>
       <c r="I15" s="20" t="inlineStr"/>
       <c r="J15" s="20" t="inlineStr"/>
@@ -8946,7 +8925,14 @@
       <c r="P15" s="20" t="inlineStr"/>
       <c r="Q15" s="20" t="inlineStr"/>
       <c r="R15" s="20" t="inlineStr"/>
-      <c r="S15" s="20" t="inlineStr"/>
+      <c r="S15" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -8954,7 +8940,7 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr"/>
@@ -8971,17 +8957,31 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="20" t="inlineStr"/>
-      <c r="Q16" s="20" t="inlineStr"/>
-      <c r="R16" s="20" t="inlineStr"/>
-      <c r="S16" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
+      <c r="P16" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q16" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
+      <c r="R16" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
       <c r="V16" s="20" t="inlineStr"/>

--- a/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
+++ b/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -7944,12 +7944,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr">
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1296万
 $38,580/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L5" s="22" t="inlineStr">
@@ -8023,10 +8023,122 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1982万
+$35,332/呎
+(26年-07月-30日)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1547万
+$35,554/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1760万
+$37,516/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1271万
+$37,821/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1700万
+$39,171/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1880万
+$36,515/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1775万
+$35,357/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5241万
+$40,500/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U6" s="23" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+$4169万
+$42,500/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="V6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7&amp;8</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>D1 | 1612呎 (4+房)
 $6287万
@@ -8034,7 +8146,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>D2 | 1642呎 (4+房)
 $7739万
@@ -8042,7 +8154,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>D3 | 1593呎 (4+房)
 $7628万
@@ -8050,7 +8162,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D5 | 1595呎 (4+房)
 $8325万
@@ -8058,7 +8170,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>D6 | 1596呎 (4+房)
 $8330万
@@ -8066,7 +8178,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>D7 | 1602呎 (4+房)
 招标单位
@@ -8074,13 +8186,13 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-      <c r="K6" s="20" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr"/>
-      <c r="M6" s="20" t="inlineStr"/>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 招标单位
@@ -8088,14 +8200,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O6" s="20" t="inlineStr"/>
-      <c r="P6" s="20" t="inlineStr"/>
-      <c r="Q6" s="20" t="inlineStr"/>
-      <c r="R6" s="20" t="inlineStr"/>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="20" t="inlineStr"/>
-      <c r="V6" s="23" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="23" t="inlineStr">
         <is>
           <t>S3 | 1608呎 (4+房)
 $9144万
@@ -8103,118 +8215,6 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1982万
-$35,332/呎
-(26年-07月-30日)</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1547万
-$35,554/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1760万
-$37,516/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K7" s="22" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1271万
-$37,821/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="L7" s="22" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1700万
-$39,171/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M7" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1880万
-$36,515/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="21" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1775万
-$35,357/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q7" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5241万
-$40,500/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U7" s="23" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-$4169万
-$42,500/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8448,12 +8448,12 @@
 (26年-07月-13日)</t>
         </is>
       </c>
-      <c r="K10" s="22" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1222万
 $36,354/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="L10" s="22" t="inlineStr">
@@ -8639,16 +8639,100 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6065万
+$38,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4687万
+$29,200/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5834万
+$37,021/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4743万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$4978万
+$31,525/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$4752万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+      <c r="K12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr"/>
+      <c r="M12" s="20" t="inlineStr"/>
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+$8387万
+$38,403/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr"/>
+      <c r="P12" s="20" t="inlineStr"/>
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6519万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1992万
@@ -8656,15 +8740,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I12" s="23" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1432万
 $32,931/呎
-(26年-07月-21日)</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
+(26年-08月-14日)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1618万
@@ -8672,7 +8756,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>E5 | 298呎 (1房)
 $1010万
@@ -8680,7 +8764,7 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="L12" s="21" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t>E6 | 397呎 (2房)
 $1633万
@@ -8688,7 +8772,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M12" s="23" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t>E7 | 477呎 (2房)
 $1797万
@@ -8696,8 +8780,8 @@
 (26年-07月-23日)</t>
         </is>
       </c>
-      <c r="N12" s="20" t="inlineStr"/>
-      <c r="O12" s="21" t="inlineStr">
+      <c r="N13" s="20" t="inlineStr"/>
+      <c r="O13" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8705,7 +8789,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P12" s="23" t="inlineStr">
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1648万
@@ -8713,7 +8797,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="Q12" s="21" t="inlineStr">
+      <c r="Q13" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8721,7 +8805,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R12" s="23" t="inlineStr">
+      <c r="R13" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $4670万
@@ -8729,8 +8813,8 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="23" t="inlineStr">
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5694万
@@ -8738,7 +8822,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U12" s="21" t="inlineStr">
+      <c r="U13" s="21" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8746,146 +8830,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>2&amp;3</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6065万
-$38,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4687万
-$29,200/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5834万
-$37,021/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4743万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$4978万
-$31,525/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$4752万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr"/>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
-      <c r="K13" s="20" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr"/>
-      <c r="M13" s="20" t="inlineStr"/>
-      <c r="N13" s="23" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-$8387万
-$38,403/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="O13" s="20" t="inlineStr"/>
-      <c r="P13" s="20" t="inlineStr"/>
-      <c r="Q13" s="20" t="inlineStr"/>
-      <c r="R13" s="20" t="inlineStr"/>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="20" t="inlineStr"/>
-      <c r="U13" s="20" t="inlineStr"/>
-      <c r="V13" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6519万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+      <c r="V13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>B&amp;G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8897,7 +8855,14 @@
       <c r="P14" s="20" t="inlineStr"/>
       <c r="Q14" s="20" t="inlineStr"/>
       <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="20" t="inlineStr"/>
+      <c r="S14" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -8905,15 +8870,57 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr"/>
-      <c r="C15" s="20" t="inlineStr"/>
-      <c r="D15" s="20" t="inlineStr"/>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H15" s="20" t="inlineStr"/>
       <c r="I15" s="20" t="inlineStr"/>
       <c r="J15" s="20" t="inlineStr"/>
@@ -8925,14 +8932,7 @@
       <c r="P15" s="20" t="inlineStr"/>
       <c r="Q15" s="20" t="inlineStr"/>
       <c r="R15" s="20" t="inlineStr"/>
-      <c r="S15" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
+      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>

--- a/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
+++ b/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
@@ -2394,7 +2394,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -8037,7 +8037,7 @@
           <t>E1 | 561呎 (2房)
 $1982万
 $35,332/呎
-(26年-07月-30日)</t>
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -8331,10 +8331,122 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1905万
+$33,961/呎
+(26年-07月-27日)</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1487万
+$34,175/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1547万
+$32,991/呎
+(26年-07月-13日)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1222万
+$36,354/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1634万
+$37,650/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1807万
+$35,095/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr"/>
+      <c r="O9" s="23" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+$4002万
+$41,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1710万
+$34,066/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="Q9" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$3859万
+$34,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5823万
+$45,000/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U9" s="21" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5&amp;6</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>D1 | 1596呎 (4+房)
 $6384万
@@ -8342,7 +8454,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>D2 | 1605呎 (4+房)
 $4815万
@@ -8350,7 +8462,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>D3 | 1576呎 (4+房)
 $5358万
@@ -8358,7 +8470,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D5 | 1581呎 (4+房)
 $4933万
@@ -8366,7 +8478,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>D6 | 1579呎 (4+房)
 $5211万
@@ -8374,7 +8486,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>D7 | 1584呎 (4+房)
 $6019万
@@ -8382,13 +8494,13 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-      <c r="K9" s="20" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr"/>
-      <c r="M9" s="20" t="inlineStr"/>
-      <c r="N9" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t>G1 | 2185呎 (4+房)
 招标单位
@@ -8396,14 +8508,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O9" s="20" t="inlineStr"/>
-      <c r="P9" s="20" t="inlineStr"/>
-      <c r="Q9" s="20" t="inlineStr"/>
-      <c r="R9" s="20" t="inlineStr"/>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="20" t="inlineStr"/>
-      <c r="U9" s="20" t="inlineStr"/>
-      <c r="V9" s="23" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="23" t="inlineStr">
         <is>
           <t>S3 | 1590呎 (4+房)
 $6678万
@@ -8411,118 +8523,6 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1905万
-$33,961/呎
-(26年-07月-27日)</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1487万
-$34,175/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1547万
-$32,991/呎
-(26年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="K10" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1222万
-$36,354/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L10" s="22" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1634万
-$37,650/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M10" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1807万
-$35,095/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="N10" s="20" t="inlineStr"/>
-      <c r="O10" s="23" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-$4002万
-$41,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="P10" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1710万
-$34,066/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="Q10" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R10" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$3859万
-$34,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5823万
-$45,000/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U10" s="21" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -8835,15 +8835,57 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8855,14 +8897,7 @@
       <c r="P14" s="20" t="inlineStr"/>
       <c r="Q14" s="20" t="inlineStr"/>
       <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
+      <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -8870,57 +8905,15 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr"/>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
       <c r="H15" s="20" t="inlineStr"/>
       <c r="I15" s="20" t="inlineStr"/>
       <c r="J15" s="20" t="inlineStr"/>
@@ -8929,9 +8922,30 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="20" t="inlineStr"/>
-      <c r="Q15" s="20" t="inlineStr"/>
-      <c r="R15" s="20" t="inlineStr"/>
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q15" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
       <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
@@ -8940,7 +8954,7 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B&amp;G&amp;1</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr"/>
@@ -8957,31 +8971,17 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q16" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
+      <c r="P16" s="20" t="inlineStr"/>
+      <c r="Q16" s="20" t="inlineStr"/>
+      <c r="R16" s="20" t="inlineStr"/>
+      <c r="S16" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="R16" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
       <c r="V16" s="20" t="inlineStr"/>

--- a/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
+++ b/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
@@ -6140,7 +6140,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -8023,16 +8023,100 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7&amp;8</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1612呎 (4+房)
+$6287万
+$39,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1642呎 (4+房)
+$7739万
+$47,132/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1593呎 (4+房)
+$7628万
+$47,883/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1595呎 (4+房)
+$8325万
+$52,194/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1596呎 (4+房)
+$8330万
+$52,193/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>D7 | 1602呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1608呎 (4+房)
+$9144万
+$56,866/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1982万
@@ -8040,7 +8124,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1547万
@@ -8048,7 +8132,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1760万
@@ -8056,7 +8140,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1271万
@@ -8064,7 +8148,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1700万
@@ -8072,7 +8156,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1880万
@@ -8080,8 +8164,8 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="21" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8089,7 +8173,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1775万
@@ -8097,7 +8181,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="Q6" s="21" t="inlineStr">
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8105,7 +8189,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R6" s="21" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 招标单位
@@ -8113,8 +8197,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="23" t="inlineStr">
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5241万
@@ -8122,7 +8206,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U6" s="23" t="inlineStr">
+      <c r="U7" s="23" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 $4169万
@@ -8130,91 +8214,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="V6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7&amp;8</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1612呎 (4+房)
-$6287万
-$39,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1642呎 (4+房)
-$7739万
-$47,132/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1593呎 (4+房)
-$7628万
-$47,883/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1595呎 (4+房)
-$8325万
-$52,194/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1596呎 (4+房)
-$8330万
-$52,193/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>D7 | 1602呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
-      <c r="K7" s="20" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr"/>
-      <c r="M7" s="20" t="inlineStr"/>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O7" s="20" t="inlineStr"/>
-      <c r="P7" s="20" t="inlineStr"/>
-      <c r="Q7" s="20" t="inlineStr"/>
-      <c r="R7" s="20" t="inlineStr"/>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="20" t="inlineStr"/>
-      <c r="U7" s="20" t="inlineStr"/>
-      <c r="V7" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1608呎 (4+房)
-$9144万
-$56,866/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8639,10 +8639,122 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1992万
+$35,499/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1432万
+$32,931/呎
+(26年-08月-14日)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1618万
+$34,490/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>E5 | 298呎 (1房)
+$1010万
+$33,903/呎
+(26年-08月-12日)</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>E6 | 397呎 (2房)
+$1633万
+$41,141/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M12" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 477呎 (2房)
+$1797万
+$37,665/呎
+(26年-08月-19日)</t>
+        </is>
+      </c>
+      <c r="N12" s="20" t="inlineStr"/>
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P12" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1648万
+$32,825/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="Q12" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R12" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$4670万
+$41,143/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5694万
+$44,000/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U12" s="21" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>2&amp;3</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>D1 | 1596呎 (4+房)
 $6065万
@@ -8650,7 +8762,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>D2 | 1605呎 (4+房)
 $4687万
@@ -8658,7 +8770,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>D3 | 1576呎 (4+房)
 $5834万
@@ -8666,7 +8778,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D5 | 1581呎 (4+房)
 $4743万
@@ -8674,7 +8786,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>D6 | 1579呎 (4+房)
 $4978万
@@ -8682,7 +8794,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>D7 | 1584呎 (4+房)
 $4752万
@@ -8690,13 +8802,13 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-      <c r="K12" s="20" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr"/>
-      <c r="M12" s="20" t="inlineStr"/>
-      <c r="N12" s="23" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
+      <c r="K13" s="20" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr"/>
+      <c r="M13" s="20" t="inlineStr"/>
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 $8387万
@@ -8704,14 +8816,14 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="O12" s="20" t="inlineStr"/>
-      <c r="P12" s="20" t="inlineStr"/>
-      <c r="Q12" s="20" t="inlineStr"/>
-      <c r="R12" s="20" t="inlineStr"/>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="20" t="inlineStr"/>
-      <c r="U12" s="20" t="inlineStr"/>
-      <c r="V12" s="23" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr"/>
+      <c r="P13" s="20" t="inlineStr"/>
+      <c r="Q13" s="20" t="inlineStr"/>
+      <c r="R13" s="20" t="inlineStr"/>
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="20" t="inlineStr"/>
+      <c r="U13" s="20" t="inlineStr"/>
+      <c r="V13" s="23" t="inlineStr">
         <is>
           <t>S3 | 1590呎 (4+房)
 $6519万
@@ -8720,172 +8832,18 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="20" t="inlineStr"/>
-      <c r="D13" s="20" t="inlineStr"/>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1992万
-$35,499/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I13" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1432万
-$32,931/呎
-(26年-08月-14日)</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1618万
-$34,490/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K13" s="23" t="inlineStr">
-        <is>
-          <t>E5 | 298呎 (1房)
-$1010万
-$33,903/呎
-(26年-08月-12日)</t>
-        </is>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t>E6 | 397呎 (2房)
-$1633万
-$41,141/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M13" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 477呎 (2房)
-$1797万
-$37,665/呎
-(26年-07月-23日)</t>
-        </is>
-      </c>
-      <c r="N13" s="20" t="inlineStr"/>
-      <c r="O13" s="21" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P13" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1648万
-$32,825/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="Q13" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R13" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$4670万
-$41,143/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5694万
-$44,000/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U13" s="21" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V13" s="20" t="inlineStr"/>
-    </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8894,9 +8852,30 @@
       <c r="M14" s="20" t="inlineStr"/>
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="20" t="inlineStr"/>
-      <c r="Q14" s="20" t="inlineStr"/>
-      <c r="R14" s="20" t="inlineStr"/>
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q14" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R14" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
       <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
@@ -8905,7 +8884,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B&amp;G&amp;1</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr"/>
@@ -8922,31 +8901,17 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q15" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
+      <c r="P15" s="20" t="inlineStr"/>
+      <c r="Q15" s="20" t="inlineStr"/>
+      <c r="R15" s="20" t="inlineStr"/>
+      <c r="S15" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="R15" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -8954,15 +8919,57 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8974,14 +8981,7 @@
       <c r="P16" s="20" t="inlineStr"/>
       <c r="Q16" s="20" t="inlineStr"/>
       <c r="R16" s="20" t="inlineStr"/>
-      <c r="S16" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
+      <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
       <c r="V16" s="20" t="inlineStr"/>

--- a/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
+++ b/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
@@ -8023,10 +8023,122 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1982万
+$35,332/呎
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1547万
+$35,554/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1760万
+$37,516/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1271万
+$37,821/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1700万
+$39,171/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1880万
+$36,515/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1775万
+$35,357/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5241万
+$40,500/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U6" s="23" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+$4169万
+$42,500/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="V6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7&amp;8</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>D1 | 1612呎 (4+房)
 $6287万
@@ -8034,7 +8146,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>D2 | 1642呎 (4+房)
 $7739万
@@ -8042,7 +8154,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>D3 | 1593呎 (4+房)
 $7628万
@@ -8050,7 +8162,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D5 | 1595呎 (4+房)
 $8325万
@@ -8058,7 +8170,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>D6 | 1596呎 (4+房)
 $8330万
@@ -8066,7 +8178,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>D7 | 1602呎 (4+房)
 招标单位
@@ -8074,13 +8186,13 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-      <c r="K6" s="20" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr"/>
-      <c r="M6" s="20" t="inlineStr"/>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 招标单位
@@ -8088,14 +8200,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O6" s="20" t="inlineStr"/>
-      <c r="P6" s="20" t="inlineStr"/>
-      <c r="Q6" s="20" t="inlineStr"/>
-      <c r="R6" s="20" t="inlineStr"/>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="20" t="inlineStr"/>
-      <c r="V6" s="23" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="23" t="inlineStr">
         <is>
           <t>S3 | 1608呎 (4+房)
 $9144万
@@ -8103,118 +8215,6 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1982万
-$35,332/呎
-(26年-08月-17日)</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1547万
-$35,554/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1760万
-$37,516/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1271万
-$37,821/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L7" s="22" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1700万
-$39,171/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M7" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1880万
-$36,515/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="21" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1775万
-$35,357/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q7" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5241万
-$40,500/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U7" s="23" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-$4169万
-$42,500/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
+++ b/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
@@ -8023,16 +8023,100 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7&amp;8</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1612呎 (4+房)
+$6287万
+$39,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1642呎 (4+房)
+$7739万
+$47,132/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1593呎 (4+房)
+$7628万
+$47,883/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1595呎 (4+房)
+$8325万
+$52,194/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1596呎 (4+房)
+$8330万
+$52,193/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>D7 | 1602呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1608呎 (4+房)
+$9144万
+$56,866/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1982万
@@ -8040,7 +8124,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1547万
@@ -8048,7 +8132,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1760万
@@ -8056,7 +8140,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1271万
@@ -8064,7 +8148,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1700万
@@ -8072,7 +8156,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1880万
@@ -8080,8 +8164,8 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="21" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8089,7 +8173,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1775万
@@ -8097,7 +8181,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="Q6" s="21" t="inlineStr">
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8105,7 +8189,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R6" s="21" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 招标单位
@@ -8113,8 +8197,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="23" t="inlineStr">
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5241万
@@ -8122,7 +8206,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U6" s="23" t="inlineStr">
+      <c r="U7" s="23" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 $4169万
@@ -8130,91 +8214,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="V6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7&amp;8</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1612呎 (4+房)
-$6287万
-$39,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1642呎 (4+房)
-$7739万
-$47,132/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1593呎 (4+房)
-$7628万
-$47,883/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1595呎 (4+房)
-$8325万
-$52,194/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1596呎 (4+房)
-$8330万
-$52,193/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>D7 | 1602呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
-      <c r="K7" s="20" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr"/>
-      <c r="M7" s="20" t="inlineStr"/>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O7" s="20" t="inlineStr"/>
-      <c r="P7" s="20" t="inlineStr"/>
-      <c r="Q7" s="20" t="inlineStr"/>
-      <c r="R7" s="20" t="inlineStr"/>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="20" t="inlineStr"/>
-      <c r="U7" s="20" t="inlineStr"/>
-      <c r="V7" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1608呎 (4+房)
-$9144万
-$56,866/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8331,16 +8331,100 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5&amp;6</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6384万
+$40,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4815万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5358万
+$34,000/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4933万
+$31,200/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$5211万
+$33,000/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$6019万
+$38,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+      <c r="K9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t>G1 | 2185呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr"/>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr"/>
+      <c r="V9" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6678万
+$42,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1905万
@@ -8348,7 +8432,7 @@
 (26年-07月-27日)</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1487万
@@ -8356,7 +8440,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1547万
@@ -8364,7 +8448,7 @@
 (26年-07月-13日)</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1222万
@@ -8372,7 +8456,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L9" s="22" t="inlineStr">
+      <c r="L10" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1634万
@@ -8380,7 +8464,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1807万
@@ -8388,8 +8472,8 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="23" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr"/>
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 $4002万
@@ -8397,7 +8481,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="P9" s="23" t="inlineStr">
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1710万
@@ -8405,7 +8489,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="Q9" s="21" t="inlineStr">
+      <c r="Q10" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8413,7 +8497,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R9" s="23" t="inlineStr">
+      <c r="R10" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $3859万
@@ -8421,8 +8505,8 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="23" t="inlineStr">
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5823万
@@ -8430,7 +8514,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U9" s="21" t="inlineStr">
+      <c r="U10" s="21" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8438,91 +8522,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5&amp;6</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6384万
-$40,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4815万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5358万
-$34,000/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4933万
-$31,200/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$5211万
-$33,000/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$6019万
-$38,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr"/>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
-      <c r="K10" s="20" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr"/>
-      <c r="M10" s="20" t="inlineStr"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t>G1 | 2185呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="20" t="inlineStr"/>
-      <c r="Q10" s="20" t="inlineStr"/>
-      <c r="R10" s="20" t="inlineStr"/>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="20" t="inlineStr"/>
-      <c r="U10" s="20" t="inlineStr"/>
-      <c r="V10" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6678万
-$42,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
+      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -8835,15 +8835,57 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8852,30 +8894,9 @@
       <c r="M14" s="20" t="inlineStr"/>
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q14" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R14" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="P14" s="20" t="inlineStr"/>
+      <c r="Q14" s="20" t="inlineStr"/>
+      <c r="R14" s="20" t="inlineStr"/>
       <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
@@ -8919,57 +8940,15 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8978,9 +8957,30 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="20" t="inlineStr"/>
-      <c r="Q16" s="20" t="inlineStr"/>
-      <c r="R16" s="20" t="inlineStr"/>
+      <c r="P16" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q16" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R16" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
       <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>

--- a/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
+++ b/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
@@ -8023,10 +8023,122 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1982万
+$35,332/呎
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1547万
+$35,554/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1760万
+$37,516/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1271万
+$37,821/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1700万
+$39,171/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1880万
+$36,515/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1775万
+$35,357/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5241万
+$40,500/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U6" s="23" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+$4169万
+$42,500/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="V6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7&amp;8</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>D1 | 1612呎 (4+房)
 $6287万
@@ -8034,7 +8146,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>D2 | 1642呎 (4+房)
 $7739万
@@ -8042,7 +8154,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>D3 | 1593呎 (4+房)
 $7628万
@@ -8050,7 +8162,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D5 | 1595呎 (4+房)
 $8325万
@@ -8058,7 +8170,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>D6 | 1596呎 (4+房)
 $8330万
@@ -8066,7 +8178,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>D7 | 1602呎 (4+房)
 招标单位
@@ -8074,13 +8186,13 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-      <c r="K6" s="20" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr"/>
-      <c r="M6" s="20" t="inlineStr"/>
-      <c r="N6" s="21" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 招标单位
@@ -8088,14 +8200,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O6" s="20" t="inlineStr"/>
-      <c r="P6" s="20" t="inlineStr"/>
-      <c r="Q6" s="20" t="inlineStr"/>
-      <c r="R6" s="20" t="inlineStr"/>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="20" t="inlineStr"/>
-      <c r="U6" s="20" t="inlineStr"/>
-      <c r="V6" s="23" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="23" t="inlineStr">
         <is>
           <t>S3 | 1608呎 (4+房)
 $9144万
@@ -8103,118 +8215,6 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1982万
-$35,332/呎
-(26年-08月-17日)</t>
-        </is>
-      </c>
-      <c r="I7" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1547万
-$35,554/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1760万
-$37,516/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="K7" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1271万
-$37,821/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L7" s="22" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1700万
-$39,171/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M7" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1880万
-$36,515/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="N7" s="20" t="inlineStr"/>
-      <c r="O7" s="21" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1775万
-$35,357/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q7" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5241万
-$40,500/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U7" s="23" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-$4169万
-$42,500/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8331,10 +8331,122 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1905万
+$33,961/呎
+(26年-07月-27日)</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1487万
+$34,175/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1547万
+$32,991/呎
+(26年-07月-13日)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1222万
+$36,354/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1634万
+$37,650/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1807万
+$35,095/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr"/>
+      <c r="O9" s="23" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+$4002万
+$41,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1710万
+$34,066/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="Q9" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$3859万
+$34,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5823万
+$45,000/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U9" s="21" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5&amp;6</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>D1 | 1596呎 (4+房)
 $6384万
@@ -8342,7 +8454,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>D2 | 1605呎 (4+房)
 $4815万
@@ -8350,7 +8462,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>D3 | 1576呎 (4+房)
 $5358万
@@ -8358,7 +8470,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D5 | 1581呎 (4+房)
 $4933万
@@ -8366,7 +8478,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>D6 | 1579呎 (4+房)
 $5211万
@@ -8374,7 +8486,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>D7 | 1584呎 (4+房)
 $6019万
@@ -8382,13 +8494,13 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-      <c r="K9" s="20" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr"/>
-      <c r="M9" s="20" t="inlineStr"/>
-      <c r="N9" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t>G1 | 2185呎 (4+房)
 招标单位
@@ -8396,14 +8508,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O9" s="20" t="inlineStr"/>
-      <c r="P9" s="20" t="inlineStr"/>
-      <c r="Q9" s="20" t="inlineStr"/>
-      <c r="R9" s="20" t="inlineStr"/>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="20" t="inlineStr"/>
-      <c r="U9" s="20" t="inlineStr"/>
-      <c r="V9" s="23" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="23" t="inlineStr">
         <is>
           <t>S3 | 1590呎 (4+房)
 $6678万
@@ -8411,118 +8523,6 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1905万
-$33,961/呎
-(26年-07月-27日)</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1487万
-$34,175/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1547万
-$32,991/呎
-(26年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="K10" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1222万
-$36,354/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L10" s="22" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1634万
-$37,650/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M10" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1807万
-$35,095/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="N10" s="20" t="inlineStr"/>
-      <c r="O10" s="23" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-$4002万
-$41,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="P10" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1710万
-$34,066/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="Q10" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R10" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$3859万
-$34,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5823万
-$45,000/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U10" s="21" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -8639,16 +8639,100 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6065万
+$38,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4687万
+$29,200/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5834万
+$37,021/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4743万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$4978万
+$31,525/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$4752万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+      <c r="K12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr"/>
+      <c r="M12" s="20" t="inlineStr"/>
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+$8387万
+$38,403/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr"/>
+      <c r="P12" s="20" t="inlineStr"/>
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6519万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1992万
@@ -8656,7 +8740,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I12" s="23" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1432万
@@ -8664,7 +8748,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1618万
@@ -8672,7 +8756,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>E5 | 298呎 (1房)
 $1010万
@@ -8680,7 +8764,7 @@
 (26年-08月-12日)</t>
         </is>
       </c>
-      <c r="L12" s="21" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t>E6 | 397呎 (2房)
 $1633万
@@ -8688,7 +8772,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M12" s="23" t="inlineStr">
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t>E7 | 477呎 (2房)
 $1797万
@@ -8696,8 +8780,8 @@
 (26年-08月-19日)</t>
         </is>
       </c>
-      <c r="N12" s="20" t="inlineStr"/>
-      <c r="O12" s="21" t="inlineStr">
+      <c r="N13" s="20" t="inlineStr"/>
+      <c r="O13" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8705,7 +8789,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P12" s="23" t="inlineStr">
+      <c r="P13" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1648万
@@ -8713,7 +8797,7 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="Q12" s="21" t="inlineStr">
+      <c r="Q13" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8721,7 +8805,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R12" s="23" t="inlineStr">
+      <c r="R13" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $4670万
@@ -8729,8 +8813,8 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="23" t="inlineStr">
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5694万
@@ -8738,7 +8822,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U12" s="21" t="inlineStr">
+      <c r="U13" s="21" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8746,146 +8830,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>2&amp;3</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6065万
-$38,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4687万
-$29,200/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5834万
-$37,021/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4743万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$4978万
-$31,525/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$4752万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr"/>
-      <c r="I13" s="20" t="inlineStr"/>
-      <c r="J13" s="20" t="inlineStr"/>
-      <c r="K13" s="20" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr"/>
-      <c r="M13" s="20" t="inlineStr"/>
-      <c r="N13" s="23" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-$8387万
-$38,403/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="O13" s="20" t="inlineStr"/>
-      <c r="P13" s="20" t="inlineStr"/>
-      <c r="Q13" s="20" t="inlineStr"/>
-      <c r="R13" s="20" t="inlineStr"/>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="20" t="inlineStr"/>
-      <c r="U13" s="20" t="inlineStr"/>
-      <c r="V13" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6519万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+      <c r="V13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>B&amp;G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr"/>
+      <c r="C14" s="20" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
+      <c r="F14" s="20" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr"/>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8897,7 +8855,14 @@
       <c r="P14" s="20" t="inlineStr"/>
       <c r="Q14" s="20" t="inlineStr"/>
       <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="20" t="inlineStr"/>
+      <c r="S14" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -8905,7 +8870,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr"/>
@@ -8922,17 +8887,31 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="20" t="inlineStr"/>
-      <c r="Q15" s="20" t="inlineStr"/>
-      <c r="R15" s="20" t="inlineStr"/>
-      <c r="S15" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q15" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>
@@ -8940,15 +8919,57 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8957,30 +8978,9 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q16" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R16" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="P16" s="20" t="inlineStr"/>
+      <c r="Q16" s="20" t="inlineStr"/>
+      <c r="R16" s="20" t="inlineStr"/>
       <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>

--- a/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
+++ b/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
@@ -8023,16 +8023,100 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>7&amp;8</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1612呎 (4+房)
+$6287万
+$39,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1642呎 (4+房)
+$7739万
+$47,132/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1593呎 (4+房)
+$7628万
+$47,883/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1595呎 (4+房)
+$8325万
+$52,194/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1596呎 (4+房)
+$8330万
+$52,193/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>D7 | 1602呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t>G1 | 2184呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1608呎 (4+房)
+$9144万
+$56,866/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1982万
@@ -8040,7 +8124,7 @@
 (26年-08月-17日)</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1547万
@@ -8048,7 +8132,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1760万
@@ -8056,7 +8140,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="K6" s="21" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1271万
@@ -8064,7 +8148,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1700万
@@ -8072,7 +8156,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1880万
@@ -8080,8 +8164,8 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr"/>
-      <c r="O6" s="21" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 招标单位
@@ -8089,7 +8173,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1775万
@@ -8097,7 +8181,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="Q6" s="21" t="inlineStr">
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8105,7 +8189,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R6" s="21" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 招标单位
@@ -8113,8 +8197,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="S6" s="20" t="inlineStr"/>
-      <c r="T6" s="23" t="inlineStr">
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5241万
@@ -8122,7 +8206,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U6" s="23" t="inlineStr">
+      <c r="U7" s="23" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 $4169万
@@ -8130,91 +8214,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="V6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>7&amp;8</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1612呎 (4+房)
-$6287万
-$39,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1642呎 (4+房)
-$7739万
-$47,132/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1593呎 (4+房)
-$7628万
-$47,883/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1595呎 (4+房)
-$8325万
-$52,194/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1596呎 (4+房)
-$8330万
-$52,193/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>D7 | 1602呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
-      <c r="I7" s="20" t="inlineStr"/>
-      <c r="J7" s="20" t="inlineStr"/>
-      <c r="K7" s="20" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr"/>
-      <c r="M7" s="20" t="inlineStr"/>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>G1 | 2184呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O7" s="20" t="inlineStr"/>
-      <c r="P7" s="20" t="inlineStr"/>
-      <c r="Q7" s="20" t="inlineStr"/>
-      <c r="R7" s="20" t="inlineStr"/>
-      <c r="S7" s="20" t="inlineStr"/>
-      <c r="T7" s="20" t="inlineStr"/>
-      <c r="U7" s="20" t="inlineStr"/>
-      <c r="V7" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1608呎 (4+房)
-$9144万
-$56,866/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="V7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -8331,16 +8331,100 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5&amp;6</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1596呎 (4+房)
+$6384万
+$40,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1605呎 (4+房)
+$4815万
+$30,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1576呎 (4+房)
+$5358万
+$34,000/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1581呎 (4+房)
+$4933万
+$31,200/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1579呎 (4+房)
+$5211万
+$33,000/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1584呎 (4+房)
+$6019万
+$38,000/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+      <c r="K9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t>G1 | 2185呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr"/>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr"/>
+      <c r="V9" s="23" t="inlineStr">
+        <is>
+          <t>S3 | 1590呎 (4+房)
+$6678万
+$42,000/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>E1 | 561呎 (2房)
 $1905万
@@ -8348,7 +8432,7 @@
 (26年-07月-27日)</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>E2 | 435呎 (2房)
 $1487万
@@ -8356,7 +8440,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>E3 | 469呎 (2房)
 $1547万
@@ -8364,7 +8448,7 @@
 (26年-07月-13日)</t>
         </is>
       </c>
-      <c r="K9" s="21" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
         <is>
           <t>E5 | 336呎 (1房)
 $1222万
@@ -8372,7 +8456,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="L9" s="22" t="inlineStr">
+      <c r="L10" s="22" t="inlineStr">
         <is>
           <t>E6 | 434呎 (2房)
 $1634万
@@ -8380,7 +8464,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t>E7 | 515呎 (2房)
 $1807万
@@ -8388,8 +8472,8 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr"/>
-      <c r="O9" s="23" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr"/>
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t>G2 | 976呎 (3房)
 $4002万
@@ -8397,7 +8481,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="P9" s="23" t="inlineStr">
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t>G3 | 502呎 (2房)
 $1710万
@@ -8405,7 +8489,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="Q9" s="21" t="inlineStr">
+      <c r="Q10" s="21" t="inlineStr">
         <is>
           <t>G5 | 867呎 (3房)
 招标单位
@@ -8413,7 +8497,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="R9" s="23" t="inlineStr">
+      <c r="R10" s="23" t="inlineStr">
         <is>
           <t>G6 | 1135呎 (4+房)
 $3859万
@@ -8421,8 +8505,8 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="23" t="inlineStr">
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t>S1 | 1294呎 (4+房)
 $5823万
@@ -8430,7 +8514,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="U9" s="21" t="inlineStr">
+      <c r="U10" s="21" t="inlineStr">
         <is>
           <t>S2 | 981呎 (3房)
 招标单位
@@ -8438,91 +8522,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="V9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5&amp;6</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1596呎 (4+房)
-$6384万
-$40,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1605呎 (4+房)
-$4815万
-$30,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1576呎 (4+房)
-$5358万
-$34,000/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1581呎 (4+房)
-$4933万
-$31,200/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1579呎 (4+房)
-$5211万
-$33,000/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1584呎 (4+房)
-$6019万
-$38,000/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr"/>
-      <c r="I10" s="20" t="inlineStr"/>
-      <c r="J10" s="20" t="inlineStr"/>
-      <c r="K10" s="20" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr"/>
-      <c r="M10" s="20" t="inlineStr"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t>G1 | 2185呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O10" s="20" t="inlineStr"/>
-      <c r="P10" s="20" t="inlineStr"/>
-      <c r="Q10" s="20" t="inlineStr"/>
-      <c r="R10" s="20" t="inlineStr"/>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="20" t="inlineStr"/>
-      <c r="U10" s="20" t="inlineStr"/>
-      <c r="V10" s="23" t="inlineStr">
-        <is>
-          <t>S3 | 1590呎 (4+房)
-$6678万
-$42,000/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
+      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -8639,10 +8639,122 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1992万
+$35,499/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1432万
+$32,931/呎
+(26年-08月-14日)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1618万
+$34,490/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>E5 | 298呎 (1房)
+$1010万
+$33,903/呎
+(26年-08月-12日)</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>E6 | 397呎 (2房)
+$1633万
+$41,141/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M12" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 477呎 (2房)
+$1797万
+$37,665/呎
+(26年-08月-19日)</t>
+        </is>
+      </c>
+      <c r="N12" s="20" t="inlineStr"/>
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P12" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1648万
+$32,825/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="Q12" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R12" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$4670万
+$41,143/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5694万
+$44,000/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U12" s="21" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>2&amp;3</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>D1 | 1596呎 (4+房)
 $6065万
@@ -8650,7 +8762,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>D2 | 1605呎 (4+房)
 $4687万
@@ -8658,7 +8770,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>D3 | 1576呎 (4+房)
 $5834万
@@ -8666,7 +8778,7 @@
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D5 | 1581呎 (4+房)
 $4743万
@@ -8674,7 +8786,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>D6 | 1579呎 (4+房)
 $4978万
@@ -8682,7 +8794,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>D7 | 1584呎 (4+房)
 $4752万
@@ -8690,13 +8802,13 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-      <c r="K12" s="20" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr"/>
-      <c r="M12" s="20" t="inlineStr"/>
-      <c r="N12" s="23" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr"/>
+      <c r="I13" s="20" t="inlineStr"/>
+      <c r="J13" s="20" t="inlineStr"/>
+      <c r="K13" s="20" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr"/>
+      <c r="M13" s="20" t="inlineStr"/>
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t>G1 | 2184呎 (4+房)
 $8387万
@@ -8704,14 +8816,14 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="O12" s="20" t="inlineStr"/>
-      <c r="P12" s="20" t="inlineStr"/>
-      <c r="Q12" s="20" t="inlineStr"/>
-      <c r="R12" s="20" t="inlineStr"/>
-      <c r="S12" s="20" t="inlineStr"/>
-      <c r="T12" s="20" t="inlineStr"/>
-      <c r="U12" s="20" t="inlineStr"/>
-      <c r="V12" s="23" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr"/>
+      <c r="P13" s="20" t="inlineStr"/>
+      <c r="Q13" s="20" t="inlineStr"/>
+      <c r="R13" s="20" t="inlineStr"/>
+      <c r="S13" s="20" t="inlineStr"/>
+      <c r="T13" s="20" t="inlineStr"/>
+      <c r="U13" s="20" t="inlineStr"/>
+      <c r="V13" s="23" t="inlineStr">
         <is>
           <t>S3 | 1590呎 (4+房)
 $6519万
@@ -8720,122 +8832,10 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="20" t="inlineStr"/>
-      <c r="D13" s="20" t="inlineStr"/>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1992万
-$35,499/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I13" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1432万
-$32,931/呎
-(26年-08月-14日)</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1618万
-$34,490/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K13" s="23" t="inlineStr">
-        <is>
-          <t>E5 | 298呎 (1房)
-$1010万
-$33,903/呎
-(26年-08月-12日)</t>
-        </is>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t>E6 | 397呎 (2房)
-$1633万
-$41,141/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M13" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 477呎 (2房)
-$1797万
-$37,665/呎
-(26年-08月-19日)</t>
-        </is>
-      </c>
-      <c r="N13" s="20" t="inlineStr"/>
-      <c r="O13" s="21" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P13" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1648万
-$32,825/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="Q13" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R13" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$4670万
-$41,143/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="S13" s="20" t="inlineStr"/>
-      <c r="T13" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5694万
-$44,000/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U13" s="21" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V13" s="20" t="inlineStr"/>
-    </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>B&amp;G&amp;1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr"/>
@@ -8852,17 +8852,31 @@
       <c r="M14" s="20" t="inlineStr"/>
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="20" t="inlineStr"/>
-      <c r="Q14" s="20" t="inlineStr"/>
-      <c r="R14" s="20" t="inlineStr"/>
-      <c r="S14" s="21" t="inlineStr">
-        <is>
-          <t>ROSA VILLA | 3058呎 (4+房)
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q14" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
+      <c r="R14" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
       <c r="V14" s="20" t="inlineStr"/>
@@ -8870,7 +8884,7 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>B&amp;G&amp;1</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr"/>
@@ -8887,31 +8901,17 @@
       <c r="M15" s="20" t="inlineStr"/>
       <c r="N15" s="20" t="inlineStr"/>
       <c r="O15" s="20" t="inlineStr"/>
-      <c r="P15" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q15" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
+      <c r="P15" s="20" t="inlineStr"/>
+      <c r="Q15" s="20" t="inlineStr"/>
+      <c r="R15" s="20" t="inlineStr"/>
+      <c r="S15" s="21" t="inlineStr">
+        <is>
+          <t>ROSA VILLA | 3058呎 (4+房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="R15" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="S15" s="20" t="inlineStr"/>
       <c r="T15" s="20" t="inlineStr"/>
       <c r="U15" s="20" t="inlineStr"/>
       <c r="V15" s="20" t="inlineStr"/>

--- a/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
+++ b/九龙-石硖尾-滶蕴/滶蕴_销控明细表.xlsx
@@ -8331,10 +8331,122 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>E1 | 561呎 (2房)
+$1905万
+$33,961/呎
+(26年-07月-27日)</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>E2 | 435呎 (2房)
+$1487万
+$34,175/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>E3 | 469呎 (2房)
+$1547万
+$32,991/呎
+(26年-07月-13日)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>E5 | 336呎 (1房)
+$1222万
+$36,354/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L9" s="22" t="inlineStr">
+        <is>
+          <t>E6 | 434呎 (2房)
+$1634万
+$37,650/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
+        <is>
+          <t>E7 | 515呎 (2房)
+$1807万
+$35,095/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr"/>
+      <c r="O9" s="23" t="inlineStr">
+        <is>
+          <t>G2 | 976呎 (3房)
+$4002万
+$41,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 502呎 (2房)
+$1710万
+$34,066/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="Q9" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 867呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1135呎 (4+房)
+$3859万
+$34,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="23" t="inlineStr">
+        <is>
+          <t>S1 | 1294呎 (4+房)
+$5823万
+$45,000/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="U9" s="21" t="inlineStr">
+        <is>
+          <t>S2 | 981呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="V9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>5&amp;6</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>D1 | 1596呎 (4+房)
 $6384万
@@ -8342,7 +8454,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>D2 | 1605呎 (4+房)
 $4815万
@@ -8350,7 +8462,7 @@
 (26年-06月-25日)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>D3 | 1576呎 (4+房)
 $5358万
@@ -8358,7 +8470,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D5 | 1581呎 (4+房)
 $4933万
@@ -8366,7 +8478,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>D6 | 1579呎 (4+房)
 $5211万
@@ -8374,7 +8486,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>D7 | 1584呎 (4+房)
 $6019万
@@ -8382,13 +8494,13 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-      <c r="K9" s="20" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr"/>
-      <c r="M9" s="20" t="inlineStr"/>
-      <c r="N9" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t>G1 | 2185呎 (4+房)
 招标单位
@@ -8396,14 +8508,14 @@
 (在售)</t>
         </is>
       </c>
-      <c r="O9" s="20" t="inlineStr"/>
-      <c r="P9" s="20" t="inlineStr"/>
-      <c r="Q9" s="20" t="inlineStr"/>
-      <c r="R9" s="20" t="inlineStr"/>
-      <c r="S9" s="20" t="inlineStr"/>
-      <c r="T9" s="20" t="inlineStr"/>
-      <c r="U9" s="20" t="inlineStr"/>
-      <c r="V9" s="23" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="23" t="inlineStr">
         <is>
           <t>S3 | 1590呎 (4+房)
 $6678万
@@ -8411,118 +8523,6 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>E1 | 561呎 (2房)
-$1905万
-$33,961/呎
-(26年-07月-27日)</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>E2 | 435呎 (2房)
-$1487万
-$34,175/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t>E3 | 469呎 (2房)
-$1547万
-$32,991/呎
-(26年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="K10" s="21" t="inlineStr">
-        <is>
-          <t>E5 | 336呎 (1房)
-$1222万
-$36,354/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L10" s="22" t="inlineStr">
-        <is>
-          <t>E6 | 434呎 (2房)
-$1634万
-$37,650/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="M10" s="23" t="inlineStr">
-        <is>
-          <t>E7 | 515呎 (2房)
-$1807万
-$35,095/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="N10" s="20" t="inlineStr"/>
-      <c r="O10" s="23" t="inlineStr">
-        <is>
-          <t>G2 | 976呎 (3房)
-$4002万
-$41,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="P10" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 502呎 (2房)
-$1710万
-$34,066/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="Q10" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 867呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R10" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1135呎 (4+房)
-$3859万
-$34,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="S10" s="20" t="inlineStr"/>
-      <c r="T10" s="23" t="inlineStr">
-        <is>
-          <t>S1 | 1294呎 (4+房)
-$5823万
-$45,000/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="U10" s="21" t="inlineStr">
-        <is>
-          <t>S2 | 981呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="V10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
@@ -8835,15 +8835,57 @@
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr"/>
-      <c r="C14" s="20" t="inlineStr"/>
-      <c r="D14" s="20" t="inlineStr"/>
-      <c r="E14" s="20" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr"/>
-      <c r="G14" s="20" t="inlineStr"/>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>D1 | 1506呎 (4+房)
+$5420万
+$35,992/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>D2 | 1514呎 (4+房)
+$5450万
+$36,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>D3 | 1488呎 (4+房)
+$5253万
+$35,300/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D5 | 1493呎 (4+房)
+$6121万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>D6 | 1491呎 (4+房)
+$5666万
+$38,000/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>D7 | 1496呎 (4+房)
+$6134万
+$41,000/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="20" t="inlineStr"/>
@@ -8852,30 +8894,9 @@
       <c r="M14" s="20" t="inlineStr"/>
       <c r="N14" s="20" t="inlineStr"/>
       <c r="O14" s="20" t="inlineStr"/>
-      <c r="P14" s="23" t="inlineStr">
-        <is>
-          <t>G3 | 586呎 (2房)
-$1876万
-$32,022/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="Q14" s="21" t="inlineStr">
-        <is>
-          <t>G5 | 868呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="R14" s="23" t="inlineStr">
-        <is>
-          <t>G6 | 1142呎 (4+房)
-$4545万
-$39,800/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
+      <c r="P14" s="20" t="inlineStr"/>
+      <c r="Q14" s="20" t="inlineStr"/>
+      <c r="R14" s="20" t="inlineStr"/>
       <c r="S14" s="20" t="inlineStr"/>
       <c r="T14" s="20" t="inlineStr"/>
       <c r="U14" s="20" t="inlineStr"/>
@@ -8919,57 +8940,15 @@
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>D1 | 1506呎 (4+房)
-$5420万
-$35,992/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>D2 | 1514呎 (4+房)
-$5450万
-$36,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>D3 | 1488呎 (4+房)
-$5253万
-$35,300/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>D5 | 1493呎 (4+房)
-$6121万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>D6 | 1491呎 (4+房)
-$5666万
-$38,000/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="inlineStr">
-        <is>
-          <t>D7 | 1496呎 (4+房)
-$6134万
-$41,000/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
       <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
@@ -8978,9 +8957,30 @@
       <c r="M16" s="20" t="inlineStr"/>
       <c r="N16" s="20" t="inlineStr"/>
       <c r="O16" s="20" t="inlineStr"/>
-      <c r="P16" s="20" t="inlineStr"/>
-      <c r="Q16" s="20" t="inlineStr"/>
-      <c r="R16" s="20" t="inlineStr"/>
+      <c r="P16" s="23" t="inlineStr">
+        <is>
+          <t>G3 | 586呎 (2房)
+$1876万
+$32,022/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="Q16" s="21" t="inlineStr">
+        <is>
+          <t>G5 | 868呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="R16" s="23" t="inlineStr">
+        <is>
+          <t>G6 | 1142呎 (4+房)
+$4545万
+$39,800/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
       <c r="S16" s="20" t="inlineStr"/>
       <c r="T16" s="20" t="inlineStr"/>
       <c r="U16" s="20" t="inlineStr"/>
